--- a/3_meta-analysis/data/sheets_for_analysis/xlsx/lachman_2.xlsx
+++ b/3_meta-analysis/data/sheets_for_analysis/xlsx/lachman_2.xlsx
@@ -531,16 +531,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="G2" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="J2" t="n">
         <v>28.5</v>
@@ -569,10 +569,10 @@
         <v>36</v>
       </c>
       <c r="R2" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8590891618651629</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="3">
@@ -598,16 +598,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>61.5</v>
       </c>
       <c r="G3" t="n">
-        <v>86</v>
+        <v>86.5</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I3" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -618,10 +618,10 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
-        <v>0.401</v>
+        <v>0.42</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4736869476556477</v>
+        <v>0.462</v>
       </c>
     </row>
     <row r="4">
@@ -647,16 +647,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J4" t="n">
         <v>27.3</v>
@@ -684,15 +684,11 @@
       <c r="Q4" t="n">
         <v>24</v>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.57</v>
       </c>
     </row>
     <row r="5">
@@ -718,16 +714,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>42</v>
+        <v>42.5</v>
       </c>
       <c r="G5" t="n">
-        <v>47</v>
+        <v>47.5</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J5" t="n">
         <v>25.8</v>
@@ -755,11 +751,11 @@
       <c r="Q5" t="n">
         <v>36</v>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R5" t="n">
+        <v>1.119</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.011</v>
       </c>
     </row>
     <row r="6">
@@ -785,16 +781,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>45.5</v>
       </c>
       <c r="G6" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>27</v>
@@ -826,7 +822,7 @@
         <v>0.705</v>
       </c>
       <c r="S6" t="n">
-        <v>1.433522004450368</v>
+        <v>1.178</v>
       </c>
     </row>
     <row r="7">
@@ -852,16 +848,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="G7" t="n">
-        <v>31</v>
+        <v>31.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J7" t="n">
         <v>25.2</v>
@@ -890,10 +886,10 @@
         <v>24</v>
       </c>
       <c r="R7" t="n">
-        <v>0.644</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9505421493381073</v>
+        <v>0.869</v>
       </c>
     </row>
     <row r="8">
@@ -919,16 +915,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="G8" t="n">
-        <v>37</v>
+        <v>37.5</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -957,12 +953,10 @@
         <v>60.6</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.324</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.65</v>
       </c>
     </row>
     <row r="9">
@@ -988,16 +982,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="G9" t="n">
-        <v>46</v>
+        <v>46.5</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J9" t="n">
         <v>22.3</v>
@@ -1025,11 +1019,11 @@
       <c r="Q9" t="n">
         <v>81</v>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S9" t="n">
+        <v>2.012</v>
       </c>
     </row>
     <row r="10">
@@ -1055,16 +1049,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>43.5</v>
       </c>
       <c r="G10" t="n">
-        <v>46</v>
+        <v>46.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1092,11 +1086,11 @@
       <c r="Q10" t="n">
         <v>24</v>
       </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.011</v>
       </c>
     </row>
     <row r="11">
@@ -1122,16 +1116,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="G11" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J11" t="n">
         <v>29.8</v>
@@ -1160,12 +1154,10 @@
         <v>120</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.175</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.578</v>
       </c>
     </row>
     <row r="12">
@@ -1191,16 +1183,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="G12" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J12" t="n">
         <v>29.8</v>
@@ -1229,10 +1221,10 @@
         <v>73.2</v>
       </c>
       <c r="R12" t="n">
-        <v>0.467</v>
+        <v>0.519</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9050124966251124</v>
+        <v>0.831</v>
       </c>
     </row>
     <row r="13">
@@ -1258,16 +1250,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>30</v>
+        <v>30.5</v>
       </c>
       <c r="G13" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J13" t="n">
         <v>28</v>
@@ -1296,10 +1288,10 @@
         <v>87.09999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>0.517</v>
+        <v>0.621</v>
       </c>
       <c r="S13" t="n">
-        <v>1.252124631158585</v>
+        <v>1.065</v>
       </c>
     </row>
     <row r="14">
@@ -1325,16 +1317,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="G14" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J14" t="n">
         <v>26.5</v>
@@ -1362,11 +1354,11 @@
       <c r="Q14" t="n">
         <v>12</v>
       </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R14" t="n">
+        <v>2.714</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.024</v>
       </c>
     </row>
     <row r="15">
@@ -1392,16 +1384,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="G15" t="n">
-        <v>21</v>
+        <v>21.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>31</v>
@@ -1433,7 +1425,7 @@
         <v>1.176</v>
       </c>
       <c r="S15" t="n">
-        <v>1.452178890292709</v>
+        <v>1.201</v>
       </c>
     </row>
     <row r="16">
@@ -1459,16 +1451,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="G16" t="n">
-        <v>32</v>
+        <v>32.5</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
         <v>25.8</v>
@@ -1497,10 +1489,10 @@
         <v>31.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0.302</v>
+        <v>0.388</v>
       </c>
       <c r="S16" t="n">
-        <v>1.182821242603473</v>
+        <v>1.009</v>
       </c>
     </row>
     <row r="17">
@@ -1526,16 +1518,16 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>53</v>
+        <v>53.5</v>
       </c>
       <c r="G17" t="n">
-        <v>58</v>
+        <v>58.5</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>25</v>
@@ -1564,12 +1556,10 @@
         <v>120</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+        <v>0.358</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.644</v>
       </c>
     </row>
     <row r="18">
@@ -1595,16 +1585,16 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="G18" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="H18" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="I18" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="J18" t="n">
         <v>27</v>
@@ -1633,10 +1623,10 @@
         <v>228</v>
       </c>
       <c r="R18" t="n">
-        <v>1.738</v>
+        <v>1.668</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6175015428693976</v>
+        <v>0.598</v>
       </c>
     </row>
     <row r="19">
@@ -1662,16 +1652,16 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="G19" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>45.5</v>
@@ -1699,11 +1689,11 @@
       <c r="Q19" t="n">
         <v>204</v>
       </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+      <c r="R19" t="n">
+        <v>1</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.021</v>
       </c>
     </row>
     <row r="20">
@@ -1729,16 +1719,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="G20" t="n">
-        <v>33</v>
+        <v>33.5</v>
       </c>
       <c r="H20" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>30.1</v>
@@ -1767,10 +1757,10 @@
         <v>12</v>
       </c>
       <c r="R20" t="n">
-        <v>3.333</v>
+        <v>3.016</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7175059684872418</v>
+        <v>0.679</v>
       </c>
     </row>
     <row r="21">
@@ -1796,16 +1786,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>68</v>
+        <v>68.5</v>
       </c>
       <c r="G21" t="n">
-        <v>64</v>
+        <v>64.5</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I21" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="J21" t="n">
         <v>30</v>
@@ -1834,10 +1824,10 @@
         <v>34.5</v>
       </c>
       <c r="R21" t="n">
-        <v>0.604</v>
+        <v>0.627</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6704722559338391</v>
+        <v>0.639</v>
       </c>
     </row>
   </sheetData>
